--- a/KatalonData/EmailTextToPay/Manage_EmailText_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/Manage_EmailText_Demo.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="180">
   <si>
     <t>Result</t>
   </si>
@@ -668,6 +668,15 @@
   </si>
   <si>
     <t>Thu Jul 09 18:48:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 13:43:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 13:57:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 15:12:07 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1460,7 +1469,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
